--- a/author.xlsx
+++ b/author.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10328"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C84DF2E-BB77-C847-8D44-E2191438E869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="3800" yWindow="600" windowWidth="21800" windowHeight="12640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -22,14 +23,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="51">
   <si>
     <t>&lt;Project Name&gt;</t>
   </si>
   <si>
-    <t>Short Description</t>
-  </si>
-  <si>
     <t>Author:</t>
   </si>
   <si>
@@ -159,9 +157,6 @@
     <t>Name, Surname</t>
   </si>
   <si>
-    <t>The nice project is…</t>
-  </si>
-  <si>
     <t>Name of the module:</t>
   </si>
   <si>
@@ -178,12 +173,15 @@
   </si>
   <si>
     <t>&lt;name of the github project&gt;</t>
+  </si>
+  <si>
+    <t>Kurze Beschreibung</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -539,37 +537,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>45</v>
-      </c>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -583,279 +579,279 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1">
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
         <v>9</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
         <v>20</v>
       </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
         <v>24</v>
-      </c>
-      <c r="B50" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -863,277 +859,277 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1">
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
         <v>9</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
         <v>20</v>
       </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
         <v>24</v>
-      </c>
-      <c r="B50" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0200-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1142,280 +1138,286 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>1234567</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1">
         <v>45351</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>45594</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
         <v>9</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B47" t="s">
         <v>20</v>
       </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B50" t="s">
         <v>24</v>
-      </c>
-      <c r="B50" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0300-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{defa4170-0d19-0005-0004-bc88714345d2}" enabled="1" method="Standard" siteId="{4f455e02-c0f5-4dd7-8284-c56491661975}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/author.xlsx
+++ b/author.xlsx
@@ -3,15 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C84DF2E-BB77-C847-8D44-E2191438E869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C5D090-51CE-584A-84AF-961EADC2A988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="600" windowWidth="21800" windowHeight="12640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
     <sheet name="Student 1" sheetId="1" r:id="rId2"/>
     <sheet name="Student 2" sheetId="2" r:id="rId3"/>
-    <sheet name="Student 3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,10 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="51">
-  <si>
-    <t>&lt;Project Name&gt;</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="62">
   <si>
     <t>Author:</t>
   </si>
@@ -109,12 +105,6 @@
     <t>Matrikelnumber</t>
   </si>
   <si>
-    <t>Wings</t>
-  </si>
-  <si>
-    <t>Elmar</t>
-  </si>
-  <si>
     <t>Study Course:</t>
   </si>
   <si>
@@ -127,9 +117,6 @@
     <t>CPs:</t>
   </si>
   <si>
-    <t xml:space="preserve"> &lt;5&gt; or &lt;10&gt;</t>
-  </si>
-  <si>
     <t>&lt;Mechanical Engineering Department&gt;</t>
   </si>
   <si>
@@ -172,17 +159,62 @@
     <t>e-mail university</t>
   </si>
   <si>
-    <t>&lt;name of the github project&gt;</t>
-  </si>
-  <si>
     <t>Kurze Beschreibung</t>
+  </si>
+  <si>
+    <t>Das Projekt umfasst die Entwicklung und Realisierung eines autonomen Radarsystems zur digitalen Umfelderfassung. Als zentrale Steuerungseinheit dient der Mikrocontroller Arduino Nano 33 BLE Sense Lite.</t>
+  </si>
+  <si>
+    <t>https://github.com/WH171/Ultraschallradar_Automatisierungstechnik</t>
+  </si>
+  <si>
+    <t>Ultraschallradar</t>
+  </si>
+  <si>
+    <t>Hinrichs</t>
+  </si>
+  <si>
+    <t>Wilko</t>
+  </si>
+  <si>
+    <t>WH171</t>
+  </si>
+  <si>
+    <t>wilko.hinrichs.1@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>Maschinenbau und Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt;5&gt;</t>
+  </si>
+  <si>
+    <t>&lt;17.10.2001&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Wings, Elmar&gt;</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>albert.einstein@hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>Gerdau</t>
+  </si>
+  <si>
+    <t>Simon</t>
+  </si>
+  <si>
+    <t>Simon-Mueller-823</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,6 +254,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -240,10 +280,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -258,8 +299,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -543,29 +586,31 @@
   <sheetData>
     <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="114" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -591,38 +636,44 @@
   <sheetData>
     <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
+        <v>7026413</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -630,136 +681,139 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1">
-        <v>45351</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1">
-        <v>45594</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
         <v>6</v>
-      </c>
-      <c r="B22" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
         <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
         <v>10</v>
-      </c>
-      <c r="B25" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -767,31 +821,31 @@
     </row>
     <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -805,31 +859,31 @@
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" t="s">
         <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -840,10 +894,10 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" t="s">
         <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -853,8 +907,12 @@
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{647A3E07-4E71-2F41-82F1-AA9EBCD19527}"/>
+    <hyperlink ref="B40" r:id="rId2" xr:uid="{BA657914-4516-4A4E-A710-6C8AC3AE5C7E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -871,38 +929,41 @@
   <sheetData>
     <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C5" s="2">
-        <v>1234567</v>
+        <v>7025823</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -910,136 +971,139 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1">
-        <v>45351</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1">
-        <v>45594</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
         <v>3</v>
-      </c>
-      <c r="B19" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
         <v>6</v>
-      </c>
-      <c r="B22" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
         <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
         <v>10</v>
-      </c>
-      <c r="B25" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -1047,31 +1111,31 @@
     </row>
     <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s">
         <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -1085,31 +1149,31 @@
     </row>
     <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" t="s">
         <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -1120,295 +1184,16 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" t="s">
         <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0200-000000000000}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0200-000001000000}">
-      <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1234567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C6" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="1">
-        <v>45351</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="1">
-        <v>45594</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B15" xr:uid="{00000000-0002-0000-0300-000000000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B8" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C5D090-51CE-584A-84AF-961EADC2A988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC451E7-3EE5-4234-9341-5A895058EFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="65">
   <si>
     <t>Author:</t>
   </si>
@@ -33,9 +33,6 @@
     <t>Date of birth:</t>
   </si>
   <si>
-    <t>&lt;01.01.2000&gt;</t>
-  </si>
-  <si>
     <t>Address:</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
     <t>Supervisor workplace:</t>
   </si>
   <si>
-    <t>&lt;Einstein, Albert&gt;</t>
-  </si>
-  <si>
     <t>&lt;00494921 807-1001&gt;</t>
   </si>
   <si>
@@ -208,6 +202,21 @@
   </si>
   <si>
     <t>Simon-Mueller-823</t>
+  </si>
+  <si>
+    <t>&lt;Steinweg 20&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Hochschule Emden/Leer&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Fachbereich Technik&gt;</t>
+  </si>
+  <si>
+    <t>&lt;06.07.2002&gt;</t>
+  </si>
+  <si>
+    <t>Simon.Mueller@stud.hs-Emden-Leer.de</t>
   </si>
 </sst>
 </file>
@@ -293,13 +302,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -582,35 +591,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="33.5" x14ac:dyDescent="0.75">
+      <c r="A1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="114" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="114" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -626,68 +635,68 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="3" width="33.1640625" customWidth="1"/>
-    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.36328125" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="33.1796875" customWidth="1"/>
+    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2">
         <v>7026413</v>
       </c>
       <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C6" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>1</v>
       </c>
@@ -695,209 +704,209 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1">
         <v>46090</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1">
         <v>46196</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+      <c r="A21" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+      <c r="A37" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+      <c r="A44" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="B46" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="B50" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B50" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -919,65 +928,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2">
         <v>7025823</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>1</v>
       </c>
@@ -985,209 +997,200 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1">
         <v>46090</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1">
         <v>46196</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+      <c r="A21" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="B22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+      <c r="B23" t="s">
         <v>7</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="B25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+      <c r="A37" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+      <c r="A44" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="B47" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="B50" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B50" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1197,6 +1200,9 @@
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{5E5772C8-7D4F-4AEC-A368-2360E005785B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/author.xlsx
+++ b/author.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10613"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC451E7-3EE5-4234-9341-5A895058EFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C1BC25-3503-C045-B9DC-A5A25FBDFE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="14180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="4" r:id="rId1"/>
@@ -156,9 +156,6 @@
     <t>Kurze Beschreibung</t>
   </si>
   <si>
-    <t>Das Projekt umfasst die Entwicklung und Realisierung eines autonomen Radarsystems zur digitalen Umfelderfassung. Als zentrale Steuerungseinheit dient der Mikrocontroller Arduino Nano 33 BLE Sense Lite.</t>
-  </si>
-  <si>
     <t>https://github.com/WH171/Ultraschallradar_Automatisierungstechnik</t>
   </si>
   <si>
@@ -195,9 +192,6 @@
     <t>albert.einstein@hs-emden-leer.de</t>
   </si>
   <si>
-    <t>Gerdau</t>
-  </si>
-  <si>
     <t>Simon</t>
   </si>
   <si>
@@ -217,6 +211,12 @@
   </si>
   <si>
     <t>Simon.Mueller@stud.hs-Emden-Leer.de</t>
+  </si>
+  <si>
+    <t>Müller</t>
+  </si>
+  <si>
+    <t>Das Projekt umfasst die Entwicklung und Realisierung eines autonomen Radarsystems zur digitalen Umfelderfassung. Als zentrale Steuerungseinheit dient der Mikrocontroller Arduino Nano 33 BLE Sense.</t>
   </si>
 </sst>
 </file>
@@ -591,35 +591,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="33.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" ht="34" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="114" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="114" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -635,20 +635,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.36328125" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="33.1796875" customWidth="1"/>
-    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" customWidth="1"/>
+    <col min="2" max="2" width="31.5" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
@@ -668,35 +668,35 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
         <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
       </c>
       <c r="C5" s="2">
         <v>7026413</v>
       </c>
       <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>1</v>
       </c>
@@ -704,7 +704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>26</v>
       </c>
@@ -712,7 +712,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -720,33 +720,33 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>4</v>
       </c>
@@ -754,7 +754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
@@ -762,7 +762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -770,17 +770,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>11</v>
       </c>
@@ -788,7 +788,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>12</v>
       </c>
@@ -796,12 +796,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
@@ -809,7 +809,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
@@ -817,7 +817,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>35</v>
       </c>
@@ -825,53 +825,53 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>37</v>
       </c>
@@ -879,7 +879,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>13</v>
       </c>
@@ -887,7 +887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>16</v>
       </c>
@@ -895,13 +895,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -928,20 +928,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
@@ -961,35 +961,35 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2">
         <v>7025823</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>1</v>
       </c>
@@ -997,7 +997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>26</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -1013,41 +1013,41 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>6</v>
       </c>
@@ -1055,25 +1055,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>11</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>12</v>
       </c>
@@ -1089,43 +1089,43 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>13</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>16</v>
       </c>
@@ -1141,21 +1141,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" ht="21" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>37</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>13</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>16</v>
       </c>
@@ -1179,13 +1179,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
